--- a/data/samples/reports/sample_data_large/priorities/Lowest.xlsx
+++ b/data/samples/reports/sample_data_large/priorities/Lowest.xlsx
@@ -76,7 +76,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="7620000" cy="4762500"/>
+    <xdr:ext cx="18288000" cy="10287000"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="" descr=""/>
@@ -114,7 +114,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="7620000" cy="4762500"/>
+    <xdr:ext cx="18288000" cy="10287000"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="" descr=""/>
@@ -152,7 +152,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="7620000" cy="4762500"/>
+    <xdr:ext cx="18288000" cy="10287000"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="" descr=""/>
@@ -190,7 +190,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="7620000" cy="4762500"/>
+    <xdr:ext cx="18288000" cy="10287000"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="" descr=""/>
@@ -228,7 +228,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="7620000" cy="4762500"/>
+    <xdr:ext cx="18288000" cy="10287000"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="" descr=""/>
@@ -1012,7 +1012,7 @@
   <sheetCalcPr fullCalcOnLoad="1"/>
   <printOptions gridLines="0" headings="0" horizontalCentered="0" verticalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
-  <pageSetup/>
+  <pageSetup orientation="landscape"/>
   <headerFooter/>
   <drawing r:id="rId13"/>
 </worksheet>
@@ -1028,7 +1028,7 @@
   <sheetCalcPr fullCalcOnLoad="1"/>
   <printOptions gridLines="0" headings="0" horizontalCentered="0" verticalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
-  <pageSetup/>
+  <pageSetup orientation="landscape"/>
   <headerFooter/>
   <drawing r:id="rId14"/>
 </worksheet>
@@ -1044,7 +1044,7 @@
   <sheetCalcPr fullCalcOnLoad="1"/>
   <printOptions gridLines="0" headings="0" horizontalCentered="0" verticalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
-  <pageSetup/>
+  <pageSetup orientation="landscape"/>
   <headerFooter/>
   <drawing r:id="rId15"/>
 </worksheet>
@@ -1060,7 +1060,7 @@
   <sheetCalcPr fullCalcOnLoad="1"/>
   <printOptions gridLines="0" headings="0" horizontalCentered="0" verticalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
-  <pageSetup/>
+  <pageSetup orientation="landscape"/>
   <headerFooter/>
   <drawing r:id="rId16"/>
 </worksheet>
@@ -1076,7 +1076,7 @@
   <sheetCalcPr fullCalcOnLoad="1"/>
   <printOptions gridLines="0" headings="0" horizontalCentered="0" verticalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
-  <pageSetup/>
+  <pageSetup orientation="landscape"/>
   <headerFooter/>
   <drawing r:id="rId17"/>
 </worksheet>

--- a/data/samples/reports/sample_data_large/priorities/Lowest.xlsx
+++ b/data/samples/reports/sample_data_large/priorities/Lowest.xlsx
@@ -4,11 +4,6 @@
   <workbookPr date1904="false"/>
   <sheets>
     <sheet sheetId="1" name="Work Items" r:id="rId1"/>
-    <sheet sheetId="2" name="Aging Wip" r:id="rId2"/>
-    <sheet sheetId="3" name="Cfd Plot" r:id="rId3"/>
-    <sheet sheetId="4" name="Cycle Time Scatter" r:id="rId4"/>
-    <sheet sheetId="5" name="Forecasted Cfd Plot" r:id="rId5"/>
-    <sheet sheetId="6" name="Throughput Histogram" r:id="rId6"/>
   </sheets>
 </workbook>
 </file>
@@ -67,196 +62,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="18288000" cy="10287000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="" descr=""/>
-        <xdr:cNvPicPr>
-          <a:picLocks noSelect="1" noChangeAspect="1" noMove="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2336800" cy="2161540"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="18288000" cy="10287000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="" descr=""/>
-        <xdr:cNvPicPr>
-          <a:picLocks noSelect="1" noChangeAspect="1" noMove="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2336800" cy="2161540"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="18288000" cy="10287000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="" descr=""/>
-        <xdr:cNvPicPr>
-          <a:picLocks noSelect="1" noChangeAspect="1" noMove="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2336800" cy="2161540"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="18288000" cy="10287000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="" descr=""/>
-        <xdr:cNvPicPr>
-          <a:picLocks noSelect="1" noChangeAspect="1" noMove="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2336800" cy="2161540"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="18288000" cy="10287000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="" descr=""/>
-        <xdr:cNvPicPr>
-          <a:picLocks noSelect="1" noChangeAspect="1" noMove="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2336800" cy="2161540"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-</xdr:wsDr>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
   <sheetPr>
@@ -1000,84 +805,4 @@
   <pageSetup/>
   <headerFooter/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <sheetPr>
-    <pageSetUpPr fitToPage="0"/>
-  </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
-  <sheetData/>
-  <sheetCalcPr fullCalcOnLoad="1"/>
-  <printOptions gridLines="0" headings="0" horizontalCentered="0" verticalCentered="0"/>
-  <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape"/>
-  <headerFooter/>
-  <drawing r:id="rId13"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <sheetPr>
-    <pageSetUpPr fitToPage="0"/>
-  </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
-  <sheetData/>
-  <sheetCalcPr fullCalcOnLoad="1"/>
-  <printOptions gridLines="0" headings="0" horizontalCentered="0" verticalCentered="0"/>
-  <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape"/>
-  <headerFooter/>
-  <drawing r:id="rId14"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <sheetPr>
-    <pageSetUpPr fitToPage="0"/>
-  </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
-  <sheetData/>
-  <sheetCalcPr fullCalcOnLoad="1"/>
-  <printOptions gridLines="0" headings="0" horizontalCentered="0" verticalCentered="0"/>
-  <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape"/>
-  <headerFooter/>
-  <drawing r:id="rId15"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <sheetPr>
-    <pageSetUpPr fitToPage="0"/>
-  </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
-  <sheetData/>
-  <sheetCalcPr fullCalcOnLoad="1"/>
-  <printOptions gridLines="0" headings="0" horizontalCentered="0" verticalCentered="0"/>
-  <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape"/>
-  <headerFooter/>
-  <drawing r:id="rId16"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <sheetPr>
-    <pageSetUpPr fitToPage="0"/>
-  </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
-  <sheetData/>
-  <sheetCalcPr fullCalcOnLoad="1"/>
-  <printOptions gridLines="0" headings="0" horizontalCentered="0" verticalCentered="0"/>
-  <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape"/>
-  <headerFooter/>
-  <drawing r:id="rId17"/>
-</worksheet>
 </file>
--- a/data/samples/reports/sample_data_large/priorities/Lowest.xlsx
+++ b/data/samples/reports/sample_data_large/priorities/Lowest.xlsx
@@ -4,6 +4,11 @@
   <workbookPr date1904="false"/>
   <sheets>
     <sheet sheetId="1" name="Work Items" r:id="rId1"/>
+    <sheet sheetId="2" name="Aging Wip" r:id="rId2"/>
+    <sheet sheetId="3" name="Cfd Plot" r:id="rId3"/>
+    <sheet sheetId="4" name="Cycle Time Scatter" r:id="rId4"/>
+    <sheet sheetId="5" name="Forecasted Cfd Plot" r:id="rId5"/>
+    <sheet sheetId="6" name="Throughput Histogram" r:id="rId6"/>
   </sheets>
 </workbook>
 </file>
@@ -62,6 +67,196 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="18288000" cy="10287000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="" descr=""/>
+        <xdr:cNvPicPr>
+          <a:picLocks noSelect="1" noChangeAspect="1" noMove="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2336800" cy="2161540"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="18288000" cy="10287000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="" descr=""/>
+        <xdr:cNvPicPr>
+          <a:picLocks noSelect="1" noChangeAspect="1" noMove="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2336800" cy="2161540"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="18288000" cy="10287000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="" descr=""/>
+        <xdr:cNvPicPr>
+          <a:picLocks noSelect="1" noChangeAspect="1" noMove="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2336800" cy="2161540"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="18288000" cy="10287000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="" descr=""/>
+        <xdr:cNvPicPr>
+          <a:picLocks noSelect="1" noChangeAspect="1" noMove="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2336800" cy="2161540"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="18288000" cy="10287000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="" descr=""/>
+        <xdr:cNvPicPr>
+          <a:picLocks noSelect="1" noChangeAspect="1" noMove="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2336800" cy="2161540"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
   <sheetPr>
@@ -805,4 +1000,84 @@
   <pageSetup/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
+  <sheetData/>
+  <sheetCalcPr fullCalcOnLoad="1"/>
+  <printOptions gridLines="0" headings="0" horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape"/>
+  <headerFooter/>
+  <drawing r:id="rId13"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
+  <sheetData/>
+  <sheetCalcPr fullCalcOnLoad="1"/>
+  <printOptions gridLines="0" headings="0" horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape"/>
+  <headerFooter/>
+  <drawing r:id="rId14"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
+  <sheetData/>
+  <sheetCalcPr fullCalcOnLoad="1"/>
+  <printOptions gridLines="0" headings="0" horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape"/>
+  <headerFooter/>
+  <drawing r:id="rId15"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
+  <sheetData/>
+  <sheetCalcPr fullCalcOnLoad="1"/>
+  <printOptions gridLines="0" headings="0" horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape"/>
+  <headerFooter/>
+  <drawing r:id="rId16"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
+  <sheetData/>
+  <sheetCalcPr fullCalcOnLoad="1"/>
+  <printOptions gridLines="0" headings="0" horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape"/>
+  <headerFooter/>
+  <drawing r:id="rId17"/>
+</worksheet>
 </file>
--- a/data/samples/reports/sample_data_large/priorities/Lowest.xlsx
+++ b/data/samples/reports/sample_data_large/priorities/Lowest.xlsx
@@ -6,9 +6,10 @@
     <sheet sheetId="1" name="Work Items" r:id="rId1"/>
     <sheet sheetId="2" name="Aging Wip" r:id="rId2"/>
     <sheet sheetId="3" name="Cfd Plot" r:id="rId3"/>
-    <sheet sheetId="4" name="Cycle Time Scatter" r:id="rId4"/>
-    <sheet sheetId="5" name="Forecasted Cfd Plot" r:id="rId5"/>
-    <sheet sheetId="6" name="Throughput Histogram" r:id="rId6"/>
+    <sheet sheetId="4" name="Cycle Time Bands" r:id="rId4"/>
+    <sheet sheetId="5" name="Cycle Time Scatter" r:id="rId5"/>
+    <sheet sheetId="6" name="Forecasted Cfd Plot" r:id="rId6"/>
+    <sheet sheetId="7" name="Throughput Histogram" r:id="rId7"/>
   </sheets>
 </workbook>
 </file>
@@ -76,45 +77,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="18288000" cy="10287000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="" descr=""/>
-        <xdr:cNvPicPr>
-          <a:picLocks noSelect="1" noChangeAspect="1" noMove="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2336800" cy="2161540"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="18288000" cy="10287000"/>
+    <xdr:ext cx="5038725" cy="4667250"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="" descr=""/>
@@ -143,7 +106,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
@@ -152,7 +115,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="18288000" cy="10287000"/>
+    <xdr:ext cx="5038725" cy="4667250"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="" descr=""/>
@@ -181,7 +144,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
@@ -190,7 +153,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="18288000" cy="10287000"/>
+    <xdr:ext cx="5038725" cy="4667250"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="" descr=""/>
@@ -219,7 +182,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
@@ -228,7 +191,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="18288000" cy="10287000"/>
+    <xdr:ext cx="5038725" cy="4667250"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="" descr=""/>
@@ -257,12 +220,88 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="5038725" cy="4667250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="" descr=""/>
+        <xdr:cNvPicPr>
+          <a:picLocks noSelect="1" noChangeAspect="1" noMove="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2336800" cy="2161540"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="5038725" cy="4667250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="" descr=""/>
+        <xdr:cNvPicPr>
+          <a:picLocks noSelect="1" noChangeAspect="1" noMove="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2336800" cy="2161540"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
   <sheetPr>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:Q14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="12.100000000000001" min="1" max="1" bestFit="1" customWidth="1"/>
@@ -272,13 +311,16 @@
     <col width="14.3" min="5" max="5" bestFit="1" customWidth="1"/>
     <col width="14.3" min="6" max="6" bestFit="1" customWidth="1"/>
     <col width="15.400000000000002" min="7" max="7" bestFit="1" customWidth="1"/>
-    <col width="22.0" min="8" max="8" bestFit="1" customWidth="1"/>
-    <col width="23.1" min="9" max="9" bestFit="1" customWidth="1"/>
-    <col width="16.5" min="10" max="10" bestFit="1" customWidth="1"/>
-    <col width="17.6" min="11" max="11" bestFit="1" customWidth="1"/>
-    <col width="18.700000000000003" min="12" max="12" bestFit="1" customWidth="1"/>
-    <col width="18.700000000000003" min="13" max="13" bestFit="1" customWidth="1"/>
-    <col width="18.700000000000003" min="14" max="14" bestFit="1" customWidth="1"/>
+    <col width="13.200000000000001" min="8" max="8" bestFit="1" customWidth="1"/>
+    <col width="11.0" min="9" max="9" bestFit="1" customWidth="1"/>
+    <col width="7.700000000000001" min="10" max="10" bestFit="1" customWidth="1"/>
+    <col width="22.0" min="11" max="11" bestFit="1" customWidth="1"/>
+    <col width="23.1" min="12" max="12" bestFit="1" customWidth="1"/>
+    <col width="16.5" min="13" max="13" bestFit="1" customWidth="1"/>
+    <col width="17.6" min="14" max="14" bestFit="1" customWidth="1"/>
+    <col width="18.700000000000003" min="15" max="15" bestFit="1" customWidth="1"/>
+    <col width="18.700000000000003" min="16" max="16" bestFit="1" customWidth="1"/>
+    <col width="18.700000000000003" min="17" max="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -319,35 +361,50 @@
       </c>
       <c r="H1" s="0" t="inlineStr">
         <is>
+          <t>YYYY-Week</t>
+        </is>
+      </c>
+      <c r="I1" s="0" t="inlineStr">
+        <is>
+          <t>YYYY-MM</t>
+        </is>
+      </c>
+      <c r="J1" s="0" t="inlineStr">
+        <is>
+          <t>YYYY</t>
+        </is>
+      </c>
+      <c r="K1" s="0" t="inlineStr">
+        <is>
           <t>Cycle Time (days)</t>
         </is>
       </c>
-      <c r="I1" s="0" t="inlineStr">
+      <c r="L1" s="0" t="inlineStr">
         <is>
           <t>Current Age (days)</t>
         </is>
       </c>
-      <c r="J1" s="0" t="inlineStr">
+      <c r="M1" s="0" t="inlineStr">
         <is>
           <t>Done ≤ 1 day</t>
         </is>
       </c>
-      <c r="K1" s="0" t="inlineStr">
+      <c r="N1" s="0" t="inlineStr">
         <is>
           <t>Done ≤ 7 days</t>
         </is>
       </c>
-      <c r="L1" s="0" t="inlineStr">
+      <c r="O1" s="0" t="inlineStr">
         <is>
           <t>Done ≤ 14 days</t>
         </is>
       </c>
-      <c r="M1" s="0" t="inlineStr">
+      <c r="P1" s="0" t="inlineStr">
         <is>
           <t>Done ≤ 21 days</t>
         </is>
       </c>
-      <c r="N1" s="0" t="inlineStr">
+      <c r="Q1" s="0" t="inlineStr">
         <is>
           <t>Done ≤ 28 days</t>
         </is>
@@ -385,23 +442,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H2" s="0" t="n">
+      <c r="H2" s="0" t="inlineStr">
+        <is>
+          <t>2025-W47</t>
+        </is>
+      </c>
+      <c r="I2" s="0" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="J2" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K2" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="I2" s="0"/>
-      <c r="J2" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K2" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="L2" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L2" s="0"/>
       <c r="M2" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N2" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O2" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P2" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -437,23 +507,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H3" s="0" t="n">
+      <c r="H3" s="0" t="inlineStr">
+        <is>
+          <t>2025-W48</t>
+        </is>
+      </c>
+      <c r="I3" s="0" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="J3" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K3" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="I3" s="0"/>
-      <c r="J3" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K3" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L3" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L3" s="0"/>
       <c r="M3" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N3" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O3" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P3" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -489,23 +572,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H4" s="0" t="n">
+      <c r="H4" s="0" t="inlineStr">
+        <is>
+          <t>2025-W50</t>
+        </is>
+      </c>
+      <c r="I4" s="0" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="J4" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K4" s="0" t="n">
         <v>17</v>
       </c>
-      <c r="I4" s="0"/>
-      <c r="J4" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K4" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L4" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L4" s="0"/>
       <c r="M4" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N4" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O4" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P4" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -541,23 +637,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H5" s="0" t="n">
+      <c r="H5" s="0" t="inlineStr">
+        <is>
+          <t>2026-W03</t>
+        </is>
+      </c>
+      <c r="I5" s="0" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="J5" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K5" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="I5" s="0"/>
-      <c r="J5" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K5" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="L5" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L5" s="0"/>
       <c r="M5" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O5" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P5" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -593,23 +702,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H6" s="0" t="n">
+      <c r="H6" s="0" t="inlineStr">
+        <is>
+          <t>2026-W06</t>
+        </is>
+      </c>
+      <c r="I6" s="0" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="J6" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K6" s="0" t="n">
         <v>13</v>
       </c>
-      <c r="I6" s="0"/>
-      <c r="J6" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K6" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L6" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L6" s="0"/>
       <c r="M6" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O6" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P6" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -645,23 +767,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H7" s="0" t="n">
+      <c r="H7" s="0" t="inlineStr">
+        <is>
+          <t>2026-W06</t>
+        </is>
+      </c>
+      <c r="I7" s="0" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="J7" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K7" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="I7" s="0"/>
-      <c r="J7" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K7" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="L7" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L7" s="0"/>
       <c r="M7" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N7" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O7" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P7" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -697,23 +832,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H8" s="0" t="n">
+      <c r="H8" s="0" t="inlineStr">
+        <is>
+          <t>2026-W09</t>
+        </is>
+      </c>
+      <c r="I8" s="0" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="J8" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K8" s="0" t="n">
         <v>21</v>
       </c>
-      <c r="I8" s="0"/>
-      <c r="J8" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K8" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L8" s="0" t="b">
-        <v>0</v>
-      </c>
+      <c r="L8" s="0"/>
       <c r="M8" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O8" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P8" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -749,23 +897,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H9" s="0" t="n">
+      <c r="H9" s="0" t="inlineStr">
+        <is>
+          <t>2026-W07</t>
+        </is>
+      </c>
+      <c r="I9" s="0" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="J9" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K9" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="I9" s="0"/>
-      <c r="J9" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K9" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="L9" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L9" s="0"/>
       <c r="M9" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O9" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P9" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -801,23 +962,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H10" s="0" t="n">
+      <c r="H10" s="0" t="inlineStr">
+        <is>
+          <t>2026-W11</t>
+        </is>
+      </c>
+      <c r="I10" s="0" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="J10" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K10" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="I10" s="0"/>
-      <c r="J10" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K10" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L10" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L10" s="0"/>
       <c r="M10" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O10" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P10" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -853,23 +1027,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H11" s="0" t="n">
+      <c r="H11" s="0" t="inlineStr">
+        <is>
+          <t>2026-W11</t>
+        </is>
+      </c>
+      <c r="I11" s="0" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="J11" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K11" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="I11" s="0"/>
-      <c r="J11" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K11" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="L11" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L11" s="0"/>
       <c r="M11" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O11" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P11" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -904,14 +1091,17 @@
         </is>
       </c>
       <c r="H12" s="0"/>
-      <c r="I12" s="0" t="n">
-        <v>54</v>
-      </c>
+      <c r="I12" s="0"/>
       <c r="J12" s="0"/>
       <c r="K12" s="0"/>
-      <c r="L12" s="0"/>
+      <c r="L12" s="0" t="n">
+        <v>55</v>
+      </c>
       <c r="M12" s="0"/>
       <c r="N12" s="0"/>
+      <c r="O12" s="0"/>
+      <c r="P12" s="0"/>
+      <c r="Q12" s="0"/>
     </row>
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
@@ -944,14 +1134,17 @@
         </is>
       </c>
       <c r="H13" s="0"/>
-      <c r="I13" s="0" t="n">
-        <v>43</v>
-      </c>
+      <c r="I13" s="0"/>
       <c r="J13" s="0"/>
       <c r="K13" s="0"/>
-      <c r="L13" s="0"/>
+      <c r="L13" s="0" t="n">
+        <v>44</v>
+      </c>
       <c r="M13" s="0"/>
       <c r="N13" s="0"/>
+      <c r="O13" s="0"/>
+      <c r="P13" s="0"/>
+      <c r="Q13" s="0"/>
     </row>
     <row r="14">
       <c r="A14" s="0" t="inlineStr">
@@ -984,14 +1177,17 @@
         </is>
       </c>
       <c r="H14" s="0"/>
-      <c r="I14" s="0" t="n">
-        <v>28</v>
-      </c>
+      <c r="I14" s="0"/>
       <c r="J14" s="0"/>
       <c r="K14" s="0"/>
-      <c r="L14" s="0"/>
+      <c r="L14" s="0" t="n">
+        <v>29</v>
+      </c>
       <c r="M14" s="0"/>
       <c r="N14" s="0"/>
+      <c r="O14" s="0"/>
+      <c r="P14" s="0"/>
+      <c r="Q14" s="0"/>
     </row>
   </sheetData>
   <sheetCalcPr fullCalcOnLoad="1"/>
@@ -1003,38 +1199,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <sheetPr>
-    <pageSetUpPr fitToPage="0"/>
-  </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
-  <sheetData/>
-  <sheetCalcPr fullCalcOnLoad="1"/>
-  <printOptions gridLines="0" headings="0" horizontalCentered="0" verticalCentered="0"/>
-  <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape"/>
-  <headerFooter/>
-  <drawing r:id="rId13"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <sheetPr>
-    <pageSetUpPr fitToPage="0"/>
-  </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
-  <sheetData/>
-  <sheetCalcPr fullCalcOnLoad="1"/>
-  <printOptions gridLines="0" headings="0" horizontalCentered="0" verticalCentered="0"/>
-  <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape"/>
-  <headerFooter/>
-  <drawing r:id="rId14"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
   <sheetPr>
     <pageSetUpPr fitToPage="0"/>
@@ -1050,7 +1214,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
   <sheetPr>
     <pageSetUpPr fitToPage="0"/>
@@ -1066,7 +1230,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
   <sheetPr>
     <pageSetUpPr fitToPage="0"/>
@@ -1080,4 +1244,52 @@
   <headerFooter/>
   <drawing r:id="rId17"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
+  <sheetData/>
+  <sheetCalcPr fullCalcOnLoad="1"/>
+  <printOptions gridLines="0" headings="0" horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape"/>
+  <headerFooter/>
+  <drawing r:id="rId18"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
+  <sheetData/>
+  <sheetCalcPr fullCalcOnLoad="1"/>
+  <printOptions gridLines="0" headings="0" horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape"/>
+  <headerFooter/>
+  <drawing r:id="rId19"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
+  <sheetData/>
+  <sheetCalcPr fullCalcOnLoad="1"/>
+  <printOptions gridLines="0" headings="0" horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape"/>
+  <headerFooter/>
+  <drawing r:id="rId20"/>
+</worksheet>
 </file>
--- a/data/samples/reports/sample_data_large/priorities/Lowest.xlsx
+++ b/data/samples/reports/sample_data_large/priorities/Lowest.xlsx
@@ -1095,7 +1095,7 @@
       <c r="J12" s="0"/>
       <c r="K12" s="0"/>
       <c r="L12" s="0" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M12" s="0"/>
       <c r="N12" s="0"/>
@@ -1138,7 +1138,7 @@
       <c r="J13" s="0"/>
       <c r="K13" s="0"/>
       <c r="L13" s="0" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M13" s="0"/>
       <c r="N13" s="0"/>
@@ -1181,7 +1181,7 @@
       <c r="J14" s="0"/>
       <c r="K14" s="0"/>
       <c r="L14" s="0" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M14" s="0"/>
       <c r="N14" s="0"/>

--- a/data/samples/reports/sample_data_large/priorities/Lowest.xlsx
+++ b/data/samples/reports/sample_data_large/priorities/Lowest.xlsx
@@ -1095,7 +1095,7 @@
       <c r="J12" s="0"/>
       <c r="K12" s="0"/>
       <c r="L12" s="0" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M12" s="0"/>
       <c r="N12" s="0"/>
@@ -1138,7 +1138,7 @@
       <c r="J13" s="0"/>
       <c r="K13" s="0"/>
       <c r="L13" s="0" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M13" s="0"/>
       <c r="N13" s="0"/>
@@ -1181,7 +1181,7 @@
       <c r="J14" s="0"/>
       <c r="K14" s="0"/>
       <c r="L14" s="0" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M14" s="0"/>
       <c r="N14" s="0"/>

--- a/data/samples/reports/sample_data_large/priorities/Lowest.xlsx
+++ b/data/samples/reports/sample_data_large/priorities/Lowest.xlsx
@@ -1095,7 +1095,7 @@
       <c r="J12" s="0"/>
       <c r="K12" s="0"/>
       <c r="L12" s="0" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M12" s="0"/>
       <c r="N12" s="0"/>
@@ -1138,7 +1138,7 @@
       <c r="J13" s="0"/>
       <c r="K13" s="0"/>
       <c r="L13" s="0" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M13" s="0"/>
       <c r="N13" s="0"/>
@@ -1181,7 +1181,7 @@
       <c r="J14" s="0"/>
       <c r="K14" s="0"/>
       <c r="L14" s="0" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M14" s="0"/>
       <c r="N14" s="0"/>

--- a/data/samples/reports/sample_data_large/priorities/Lowest.xlsx
+++ b/data/samples/reports/sample_data_large/priorities/Lowest.xlsx
@@ -1095,7 +1095,7 @@
       <c r="J12" s="0"/>
       <c r="K12" s="0"/>
       <c r="L12" s="0" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M12" s="0"/>
       <c r="N12" s="0"/>
@@ -1138,7 +1138,7 @@
       <c r="J13" s="0"/>
       <c r="K13" s="0"/>
       <c r="L13" s="0" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M13" s="0"/>
       <c r="N13" s="0"/>
@@ -1181,7 +1181,7 @@
       <c r="J14" s="0"/>
       <c r="K14" s="0"/>
       <c r="L14" s="0" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M14" s="0"/>
       <c r="N14" s="0"/>

--- a/data/samples/reports/sample_data_large/priorities/Lowest.xlsx
+++ b/data/samples/reports/sample_data_large/priorities/Lowest.xlsx
@@ -1095,7 +1095,7 @@
       <c r="J12" s="0"/>
       <c r="K12" s="0"/>
       <c r="L12" s="0" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M12" s="0"/>
       <c r="N12" s="0"/>
@@ -1138,7 +1138,7 @@
       <c r="J13" s="0"/>
       <c r="K13" s="0"/>
       <c r="L13" s="0" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M13" s="0"/>
       <c r="N13" s="0"/>
@@ -1181,7 +1181,7 @@
       <c r="J14" s="0"/>
       <c r="K14" s="0"/>
       <c r="L14" s="0" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M14" s="0"/>
       <c r="N14" s="0"/>

--- a/data/samples/reports/sample_data_large/priorities/Lowest.xlsx
+++ b/data/samples/reports/sample_data_large/priorities/Lowest.xlsx
@@ -1095,7 +1095,7 @@
       <c r="J12" s="0"/>
       <c r="K12" s="0"/>
       <c r="L12" s="0" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M12" s="0"/>
       <c r="N12" s="0"/>
@@ -1138,7 +1138,7 @@
       <c r="J13" s="0"/>
       <c r="K13" s="0"/>
       <c r="L13" s="0" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M13" s="0"/>
       <c r="N13" s="0"/>
@@ -1181,7 +1181,7 @@
       <c r="J14" s="0"/>
       <c r="K14" s="0"/>
       <c r="L14" s="0" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M14" s="0"/>
       <c r="N14" s="0"/>

--- a/data/samples/reports/sample_data_large/priorities/Lowest.xlsx
+++ b/data/samples/reports/sample_data_large/priorities/Lowest.xlsx
@@ -1095,7 +1095,7 @@
       <c r="J12" s="0"/>
       <c r="K12" s="0"/>
       <c r="L12" s="0" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M12" s="0"/>
       <c r="N12" s="0"/>
@@ -1138,7 +1138,7 @@
       <c r="J13" s="0"/>
       <c r="K13" s="0"/>
       <c r="L13" s="0" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M13" s="0"/>
       <c r="N13" s="0"/>
@@ -1181,7 +1181,7 @@
       <c r="J14" s="0"/>
       <c r="K14" s="0"/>
       <c r="L14" s="0" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M14" s="0"/>
       <c r="N14" s="0"/>

--- a/data/samples/reports/sample_data_large/priorities/Lowest.xlsx
+++ b/data/samples/reports/sample_data_large/priorities/Lowest.xlsx
@@ -301,7 +301,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:Q14"/>
+  <dimension ref="A1:R14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="12.100000000000001" min="1" max="1" bestFit="1" customWidth="1"/>
@@ -316,11 +316,12 @@
     <col width="7.700000000000001" min="10" max="10" bestFit="1" customWidth="1"/>
     <col width="22.0" min="11" max="11" bestFit="1" customWidth="1"/>
     <col width="23.1" min="12" max="12" bestFit="1" customWidth="1"/>
-    <col width="16.5" min="13" max="13" bestFit="1" customWidth="1"/>
-    <col width="17.6" min="14" max="14" bestFit="1" customWidth="1"/>
-    <col width="18.700000000000003" min="15" max="15" bestFit="1" customWidth="1"/>
+    <col width="99.00000000000001" min="13" max="13" bestFit="1" customWidth="1"/>
+    <col width="16.5" min="14" max="14" bestFit="1" customWidth="1"/>
+    <col width="17.6" min="15" max="15" bestFit="1" customWidth="1"/>
     <col width="18.700000000000003" min="16" max="16" bestFit="1" customWidth="1"/>
     <col width="18.700000000000003" min="17" max="17" bestFit="1" customWidth="1"/>
+    <col width="18.700000000000003" min="18" max="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -386,25 +387,30 @@
       </c>
       <c r="M1" s="0" t="inlineStr">
         <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="N1" s="0" t="inlineStr">
+        <is>
           <t>Done ≤ 1 day</t>
         </is>
       </c>
-      <c r="N1" s="0" t="inlineStr">
+      <c r="O1" s="0" t="inlineStr">
         <is>
           <t>Done ≤ 7 days</t>
         </is>
       </c>
-      <c r="O1" s="0" t="inlineStr">
+      <c r="P1" s="0" t="inlineStr">
         <is>
           <t>Done ≤ 14 days</t>
         </is>
       </c>
-      <c r="P1" s="0" t="inlineStr">
+      <c r="Q1" s="0" t="inlineStr">
         <is>
           <t>Done ≤ 21 days</t>
         </is>
       </c>
-      <c r="Q1" s="0" t="inlineStr">
+      <c r="R1" s="0" t="inlineStr">
         <is>
           <t>Done ≤ 28 days</t>
         </is>
@@ -459,11 +465,13 @@
         <v>7</v>
       </c>
       <c r="L2" s="0"/>
-      <c r="M2" s="0" t="b">
-        <v>0</v>
+      <c r="M2" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N2" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O2" s="0" t="b">
         <v>1</v>
@@ -472,6 +480,9 @@
         <v>1</v>
       </c>
       <c r="Q2" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R2" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -524,19 +535,24 @@
         <v>9</v>
       </c>
       <c r="L3" s="0"/>
-      <c r="M3" s="0" t="b">
-        <v>0</v>
+      <c r="M3" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N3" s="0" t="b">
         <v>0</v>
       </c>
       <c r="O3" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P3" s="0" t="b">
         <v>1</v>
       </c>
       <c r="Q3" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R3" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -589,8 +605,10 @@
         <v>17</v>
       </c>
       <c r="L4" s="0"/>
-      <c r="M4" s="0" t="b">
-        <v>0</v>
+      <c r="M4" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N4" s="0" t="b">
         <v>0</v>
@@ -599,9 +617,12 @@
         <v>0</v>
       </c>
       <c r="P4" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R4" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -654,11 +675,13 @@
         <v>7</v>
       </c>
       <c r="L5" s="0"/>
-      <c r="M5" s="0" t="b">
-        <v>0</v>
+      <c r="M5" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N5" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5" s="0" t="b">
         <v>1</v>
@@ -667,6 +690,9 @@
         <v>1</v>
       </c>
       <c r="Q5" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R5" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -719,19 +745,24 @@
         <v>13</v>
       </c>
       <c r="L6" s="0"/>
-      <c r="M6" s="0" t="b">
-        <v>0</v>
+      <c r="M6" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N6" s="0" t="b">
         <v>0</v>
       </c>
       <c r="O6" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" s="0" t="b">
         <v>1</v>
       </c>
       <c r="Q6" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R6" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -784,11 +815,13 @@
         <v>3</v>
       </c>
       <c r="L7" s="0"/>
-      <c r="M7" s="0" t="b">
-        <v>0</v>
+      <c r="M7" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N7" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7" s="0" t="b">
         <v>1</v>
@@ -797,6 +830,9 @@
         <v>1</v>
       </c>
       <c r="Q7" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R7" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -849,8 +885,10 @@
         <v>21</v>
       </c>
       <c r="L8" s="0"/>
-      <c r="M8" s="0" t="b">
-        <v>0</v>
+      <c r="M8" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N8" s="0" t="b">
         <v>0</v>
@@ -859,9 +897,12 @@
         <v>0</v>
       </c>
       <c r="P8" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R8" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -914,11 +955,13 @@
         <v>2</v>
       </c>
       <c r="L9" s="0"/>
-      <c r="M9" s="0" t="b">
-        <v>0</v>
+      <c r="M9" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N9" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O9" s="0" t="b">
         <v>1</v>
@@ -927,6 +970,9 @@
         <v>1</v>
       </c>
       <c r="Q9" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R9" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -979,19 +1025,24 @@
         <v>10</v>
       </c>
       <c r="L10" s="0"/>
-      <c r="M10" s="0" t="b">
-        <v>0</v>
+      <c r="M10" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N10" s="0" t="b">
         <v>0</v>
       </c>
       <c r="O10" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P10" s="0" t="b">
         <v>1</v>
       </c>
       <c r="Q10" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R10" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1044,11 +1095,13 @@
         <v>4</v>
       </c>
       <c r="L11" s="0"/>
-      <c r="M11" s="0" t="b">
-        <v>0</v>
+      <c r="M11" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
       </c>
       <c r="N11" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O11" s="0" t="b">
         <v>1</v>
@@ -1057,6 +1110,9 @@
         <v>1</v>
       </c>
       <c r="Q11" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R11" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1097,11 +1153,16 @@
       <c r="L12" s="0" t="n">
         <v>62</v>
       </c>
-      <c r="M12" s="0"/>
+      <c r="M12" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
+      </c>
       <c r="N12" s="0"/>
       <c r="O12" s="0"/>
       <c r="P12" s="0"/>
       <c r="Q12" s="0"/>
+      <c r="R12" s="0"/>
     </row>
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
@@ -1140,11 +1201,16 @@
       <c r="L13" s="0" t="n">
         <v>51</v>
       </c>
-      <c r="M13" s="0"/>
+      <c r="M13" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
+      </c>
       <c r="N13" s="0"/>
       <c r="O13" s="0"/>
       <c r="P13" s="0"/>
       <c r="Q13" s="0"/>
+      <c r="R13" s="0"/>
     </row>
     <row r="14">
       <c r="A14" s="0" t="inlineStr">
@@ -1183,11 +1249,16 @@
       <c r="L14" s="0" t="n">
         <v>36</v>
       </c>
-      <c r="M14" s="0"/>
+      <c r="M14" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data_large.csv</t>
+        </is>
+      </c>
       <c r="N14" s="0"/>
       <c r="O14" s="0"/>
       <c r="P14" s="0"/>
       <c r="Q14" s="0"/>
+      <c r="R14" s="0"/>
     </row>
   </sheetData>
   <sheetCalcPr fullCalcOnLoad="1"/>

--- a/data/samples/reports/sample_data_large/priorities/Lowest.xlsx
+++ b/data/samples/reports/sample_data_large/priorities/Lowest.xlsx
@@ -1151,7 +1151,7 @@
       <c r="J12" s="0"/>
       <c r="K12" s="0"/>
       <c r="L12" s="0" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M12" s="0" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
       <c r="J13" s="0"/>
       <c r="K13" s="0"/>
       <c r="L13" s="0" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M13" s="0" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
       <c r="J14" s="0"/>
       <c r="K14" s="0"/>
       <c r="L14" s="0" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M14" s="0" t="inlineStr">
         <is>

--- a/data/samples/reports/sample_data_large/priorities/Lowest.xlsx
+++ b/data/samples/reports/sample_data_large/priorities/Lowest.xlsx
@@ -1151,7 +1151,7 @@
       <c r="J12" s="0"/>
       <c r="K12" s="0"/>
       <c r="L12" s="0" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M12" s="0" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
       <c r="J13" s="0"/>
       <c r="K13" s="0"/>
       <c r="L13" s="0" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M13" s="0" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
       <c r="J14" s="0"/>
       <c r="K14" s="0"/>
       <c r="L14" s="0" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M14" s="0" t="inlineStr">
         <is>

--- a/data/samples/reports/sample_data_large/priorities/Lowest.xlsx
+++ b/data/samples/reports/sample_data_large/priorities/Lowest.xlsx
@@ -1151,7 +1151,7 @@
       <c r="J12" s="0"/>
       <c r="K12" s="0"/>
       <c r="L12" s="0" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M12" s="0" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
       <c r="J13" s="0"/>
       <c r="K13" s="0"/>
       <c r="L13" s="0" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M13" s="0" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
       <c r="J14" s="0"/>
       <c r="K14" s="0"/>
       <c r="L14" s="0" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M14" s="0" t="inlineStr">
         <is>

--- a/data/samples/reports/sample_data_large/priorities/Lowest.xlsx
+++ b/data/samples/reports/sample_data_large/priorities/Lowest.xlsx
@@ -1151,7 +1151,7 @@
       <c r="J12" s="0"/>
       <c r="K12" s="0"/>
       <c r="L12" s="0" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M12" s="0" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
       <c r="J13" s="0"/>
       <c r="K13" s="0"/>
       <c r="L13" s="0" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M13" s="0" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
       <c r="J14" s="0"/>
       <c r="K14" s="0"/>
       <c r="L14" s="0" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M14" s="0" t="inlineStr">
         <is>

--- a/data/samples/reports/sample_data_large/priorities/Lowest.xlsx
+++ b/data/samples/reports/sample_data_large/priorities/Lowest.xlsx
@@ -1151,7 +1151,7 @@
       <c r="J12" s="0"/>
       <c r="K12" s="0"/>
       <c r="L12" s="0" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M12" s="0" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
       <c r="J13" s="0"/>
       <c r="K13" s="0"/>
       <c r="L13" s="0" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M13" s="0" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
       <c r="J14" s="0"/>
       <c r="K14" s="0"/>
       <c r="L14" s="0" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M14" s="0" t="inlineStr">
         <is>

--- a/data/samples/reports/sample_data_large/priorities/Lowest.xlsx
+++ b/data/samples/reports/sample_data_large/priorities/Lowest.xlsx
@@ -1151,7 +1151,7 @@
       <c r="J12" s="0"/>
       <c r="K12" s="0"/>
       <c r="L12" s="0" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M12" s="0" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
       <c r="J13" s="0"/>
       <c r="K13" s="0"/>
       <c r="L13" s="0" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M13" s="0" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
       <c r="J14" s="0"/>
       <c r="K14" s="0"/>
       <c r="L14" s="0" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M14" s="0" t="inlineStr">
         <is>

--- a/data/samples/reports/sample_data_large/priorities/Lowest.xlsx
+++ b/data/samples/reports/sample_data_large/priorities/Lowest.xlsx
@@ -1151,7 +1151,7 @@
       <c r="J12" s="0"/>
       <c r="K12" s="0"/>
       <c r="L12" s="0" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M12" s="0" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
       <c r="J13" s="0"/>
       <c r="K13" s="0"/>
       <c r="L13" s="0" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M13" s="0" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
       <c r="J14" s="0"/>
       <c r="K14" s="0"/>
       <c r="L14" s="0" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M14" s="0" t="inlineStr">
         <is>

--- a/data/samples/reports/sample_data_large/priorities/Lowest.xlsx
+++ b/data/samples/reports/sample_data_large/priorities/Lowest.xlsx
@@ -1151,7 +1151,7 @@
       <c r="J12" s="0"/>
       <c r="K12" s="0"/>
       <c r="L12" s="0" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M12" s="0" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
       <c r="J13" s="0"/>
       <c r="K13" s="0"/>
       <c r="L13" s="0" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M13" s="0" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
       <c r="J14" s="0"/>
       <c r="K14" s="0"/>
       <c r="L14" s="0" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M14" s="0" t="inlineStr">
         <is>

--- a/data/samples/reports/sample_data_large/priorities/Lowest.xlsx
+++ b/data/samples/reports/sample_data_large/priorities/Lowest.xlsx
@@ -1151,7 +1151,7 @@
       <c r="J12" s="0"/>
       <c r="K12" s="0"/>
       <c r="L12" s="0" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M12" s="0" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
       <c r="J13" s="0"/>
       <c r="K13" s="0"/>
       <c r="L13" s="0" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M13" s="0" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
       <c r="J14" s="0"/>
       <c r="K14" s="0"/>
       <c r="L14" s="0" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M14" s="0" t="inlineStr">
         <is>

--- a/data/samples/reports/sample_data_large/priorities/Lowest.xlsx
+++ b/data/samples/reports/sample_data_large/priorities/Lowest.xlsx
@@ -1151,7 +1151,7 @@
       <c r="J12" s="0"/>
       <c r="K12" s="0"/>
       <c r="L12" s="0" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M12" s="0" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
       <c r="J13" s="0"/>
       <c r="K13" s="0"/>
       <c r="L13" s="0" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M13" s="0" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
       <c r="J14" s="0"/>
       <c r="K14" s="0"/>
       <c r="L14" s="0" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M14" s="0" t="inlineStr">
         <is>

--- a/data/samples/reports/sample_data_large/priorities/Lowest.xlsx
+++ b/data/samples/reports/sample_data_large/priorities/Lowest.xlsx
@@ -1151,7 +1151,7 @@
       <c r="J12" s="0"/>
       <c r="K12" s="0"/>
       <c r="L12" s="0" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M12" s="0" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
       <c r="J13" s="0"/>
       <c r="K13" s="0"/>
       <c r="L13" s="0" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M13" s="0" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
       <c r="J14" s="0"/>
       <c r="K14" s="0"/>
       <c r="L14" s="0" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M14" s="0" t="inlineStr">
         <is>
